--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2019_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2019_nuble.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:03</t>
+    <t xml:space="preserve">2026-09-24 00:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -952,7 +952,7 @@
         <v>0.08</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.06</v>
@@ -975,7 +975,7 @@
         <v>0.13</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.15</v>
@@ -998,7 +998,7 @@
         <v>-0.1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.55</v>
